--- a/AAII_Financials/Yearly/AMSSY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMSSY_YR_FIN.xlsx
@@ -2902,10 +2902,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>349900</v>
+        <v>348700</v>
       </c>
       <c r="E83" s="3">
-        <v>308500</v>
+        <v>309600</v>
       </c>
       <c r="F83" s="3">
         <v>364800</v>
